--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/01_Mandat/04_Beteiligte_Kontakte.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/01_Mandat/04_Beteiligte_Kontakte.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beteiligte" sheetId="1" r:id="Rc8d8279493eb494c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kommunikation" sheetId="2" r:id="Rc91d2da1ef584a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beteiligte" sheetId="1" r:id="Rf1d283e18bc44ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kommunikation" sheetId="2" r:id="R9172d0a9f682428e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/01_Mandat/04_Beteiligte_Kontakte.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/01_Mandat/04_Beteiligte_Kontakte.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beteiligte" sheetId="1" r:id="Rf1d283e18bc44ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kommunikation" sheetId="2" r:id="R9172d0a9f682428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beteiligte" sheetId="1" r:id="R84862207e6144d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kommunikation" sheetId="2" r:id="Rf836365cbfd84bea"/>
   </x:sheets>
 </x:workbook>
 </file>
